--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513663_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513663_FASEFINALBFFB3_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4805</v>
+        <v>4.8484</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2361</v>
+        <v>4.298</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2444</v>
+        <v>0.5505</v>
       </c>
       <c r="G2" t="n">
         <v>0.5719</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3554</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0462</v>
+        <v>0.108</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3093</v>
+        <v>0.6153</v>
       </c>
       <c r="V2" t="n">
         <v>3.9426</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9172</v>
+        <v>4.8043</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3408</v>
+        <v>5.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4236</v>
+        <v>-0.3958</v>
       </c>
       <c r="G3" t="n">
         <v>3.0329</v>
@@ -688,13 +688,13 @@
         <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3368</v>
+        <v>0.5503</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0512</v>
+        <v>-0.192</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7144</v>
+        <v>0.7422</v>
       </c>
       <c r="V3" t="n">
         <v>1.2211</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3832</v>
+        <v>3.7997</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9716</v>
+        <v>2.3325</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4116</v>
+        <v>1.4672</v>
       </c>
       <c r="G4" t="n">
         <v>3.0953</v>
@@ -766,13 +766,13 @@
         <v>0.3895</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4327</v>
+        <v>-0.0162</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5565</v>
+        <v>-0.1957</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1238</v>
+        <v>0.1795</v>
       </c>
       <c r="V4" t="n">
         <v>0.3311</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2716</v>
+        <v>2.9617</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0522</v>
+        <v>2.0762</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2194</v>
+        <v>0.8855</v>
       </c>
       <c r="G5" t="n">
         <v>1.2254</v>
@@ -844,13 +844,13 @@
         <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9352</v>
+        <v>1.6253</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4015</v>
+        <v>0.4255</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5337</v>
+        <v>1.1998</v>
       </c>
       <c r="V5" t="n">
         <v>0.89</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1462</v>
+        <v>1.939</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0772</v>
+        <v>2.5377</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06909999999999999</v>
+        <v>-0.5988</v>
       </c>
       <c r="G6" t="n">
         <v>0.9428</v>
@@ -922,13 +922,13 @@
         <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8072</v>
+        <v>0.5999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.096</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3637</v>
+        <v>0.6959</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3826</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0109</v>
+        <v>1.1103</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2579</v>
+        <v>1.5837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.753</v>
+        <v>-0.4734</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.066</v>
+        <v>1.4101</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0898</v>
+        <v>0.5316</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0238</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2694</v>
+        <v>1.7074</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0668</v>
+        <v>0.4105</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2026</v>
+        <v>1.2968</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3354</v>
+        <v>-0.2973</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1565</v>
+        <v>0.1211</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1788</v>
+        <v>-0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3632</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>-0.2997</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9358</v>
+        <v>-0.1237</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5042</v>
+        <v>-0.1761</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0825</v>
+        <v>0.5043</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5837</v>
+        <v>-0.9747</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5012</v>
+        <v>1.4789</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4101</v>
+        <v>0.3658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5316</v>
+        <v>-1.0037</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.3695</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7074</v>
+        <v>-0.5935</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4105</v>
+        <v>-1.1853</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2968</v>
+        <v>0.5918</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2973</v>
+        <v>0.9593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1211</v>
+        <v>0.1816</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4184</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3275</v>
+        <v>-0.4458</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1237</v>
+        <v>-0.3812</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2039</v>
+        <v>-0.0646</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0321</v>
+        <v>0.0451</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3355</v>
+        <v>-0.0618</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3676</v>
+        <v>0.1069</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3658</v>
+        <v>0.1934</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0037</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3695</v>
+        <v>0.2658</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5935</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1853</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5918</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9593</v>
+        <v>0.1934</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1816</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.2658</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9179</v>
+        <v>-0.1484</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.742</v>
+        <v>-0.0618</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1759</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0173</v>
+        <v>-0.0367</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0618</v>
+        <v>-0.8731</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0791</v>
+        <v>0.8365</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1934</v>
+        <v>-0.066</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0898</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2658</v>
+        <v>0.0238</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.2694</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0668</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.2026</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1934</v>
+        <v>-0.3354</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1565</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2658</v>
+        <v>-0.1788</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1762</v>
+        <v>1.3925</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0618</v>
+        <v>0.8048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1144</v>
+        <v>0.5877</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1078</v>
+        <v>-0.447</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6346</v>
+        <v>-1.3355</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5268</v>
+        <v>0.8885</v>
       </c>
       <c r="G12" t="n">
         <v>-0.735</v>
@@ -1390,13 +1390,13 @@
         <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.847</v>
+        <v>-0.1862</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6183</v>
+        <v>-0.3193</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2286</v>
+        <v>0.1331</v>
       </c>
       <c r="V12" t="n">
         <v>0.2795</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2614</v>
+        <v>-1.6772</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6626</v>
+        <v>-1.8001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4012</v>
+        <v>0.123</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3013</v>
@@ -1468,13 +1468,13 @@
         <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5394</v>
+        <v>1.1237</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5252</v>
+        <v>0.3876</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0143</v>
+        <v>0.736</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3311</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.1002</v>
+        <v>-3.3614</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2607</v>
+        <v>-2.8002</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8395</v>
+        <v>-0.5612</v>
       </c>
       <c r="G14" t="n">
         <v>-8.1275</v>
@@ -1546,13 +1546,13 @@
         <v>1.7526</v>
       </c>
       <c r="S14" t="n">
-        <v>-0</v>
+        <v>0.7388</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.263</v>
+        <v>0.1975</v>
       </c>
       <c r="U14" t="n">
-        <v>0.263</v>
+        <v>0.5413</v>
       </c>
       <c r="V14" t="n">
         <v>4.2221</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.18</v>
+        <v>14.7984</v>
       </c>
       <c r="E15" t="n">
-        <v>9.872199999999999</v>
+        <v>10.4906</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3079</v>
+        <v>4.3078</v>
       </c>
       <c r="G15" t="n">
         <v>0.9157000000000028</v>
@@ -1603,7 +1603,7 @@
         <v>5.447699999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>4.946599999999998</v>
+        <v>4.9466</v>
       </c>
       <c r="M15" t="n">
         <v>-9.479100000000001</v>
@@ -1612,7 +1612,7 @@
         <v>-5.0653</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.413600000000001</v>
+        <v>-4.4136</v>
       </c>
       <c r="P15" t="n">
         <v>-1.9474</v>
@@ -1624,13 +1624,13 @@
         <v>11.6841</v>
       </c>
       <c r="S15" t="n">
-        <v>5.0391</v>
+        <v>5.6575</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06430000000000008</v>
+        <v>0.5537</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1036</v>
+        <v>5.103599999999999</v>
       </c>
       <c r="V15" t="n">
         <v>10.1727</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0018</v>
+        <v>2.3225</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4343</v>
+        <v>2.8117</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5674</v>
+        <v>-0.4892</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9132</v>
+        <v>2.8087</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.819</v>
+        <v>1.0643</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0942</v>
+        <v>1.7444</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4199</v>
+        <v>4.2007</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.023</v>
+        <v>1.0879</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3969</v>
+        <v>3.1128</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4933</v>
+        <v>-1.392</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.796</v>
+        <v>-0.0236</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6973</v>
+        <v>-1.3684</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.1947</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9737</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.9474</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0493</v>
+        <v>-0.2914</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3595</v>
+        <v>-0.4153</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6898</v>
+        <v>0.1239</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8394</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4421</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7083</v>
+        <v>1.1333</v>
       </c>
       <c r="E17" t="n">
-        <v>2.114</v>
+        <v>-0.6509</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4057</v>
+        <v>1.7842</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8087</v>
+        <v>1.4563</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0643</v>
+        <v>0.6589</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7444</v>
+        <v>0.7974</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2007</v>
+        <v>0.9366</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0879</v>
+        <v>0.9366</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1128</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.392</v>
+        <v>0.5198</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0236</v>
+        <v>-0.2776</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3684</v>
+        <v>0.7974</v>
       </c>
       <c r="P17" t="n">
         <v>-0.1947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.1283</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.113</v>
+        <v>-0.419</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2074</v>
+        <v>0.2907</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1566</v>
+        <v>0.1611</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8502</v>
+        <v>0.0389</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0068</v>
+        <v>0.1222</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4563</v>
+        <v>-1.9132</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6589</v>
+        <v>-0.819</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7974</v>
+        <v>-1.0942</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9366</v>
+        <v>-0.4199</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9366</v>
+        <v>-0.023</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.3969</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5198</v>
+        <v>-1.4933</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2776</v>
+        <v>-0.796</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7974</v>
+        <v>-0.6973</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1684</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
         <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.105</v>
+        <v>0.2086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6183</v>
+        <v>-0.036</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5133</v>
+        <v>0.2446</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.8394</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5226</v>
+        <v>-0.1795</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4951</v>
+        <v>-1.0964</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9725</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4622</v>
@@ -1936,13 +1936,13 @@
         <v>1.9474</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6845</v>
+        <v>-1.3415</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5459</v>
+        <v>-1.1472</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1386</v>
+        <v>-0.1943</v>
       </c>
       <c r="V19" t="n">
         <v>0.06619999999999999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1832</v>
+        <v>-1.0161</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9183</v>
+        <v>-0.4796</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2649</v>
+        <v>-0.5365</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.621</v>
+        <v>2.0968</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6127</v>
+        <v>0.6861</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2337</v>
+        <v>1.4107</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5039</v>
+        <v>2.2598</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0468</v>
+        <v>1.6268</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5429</v>
+        <v>0.633</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1249</v>
+        <v>-0.163</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4342</v>
+        <v>-0.9407</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6907</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9737</v>
+        <v>-2.3368</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7526</v>
+        <v>2.3368</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7822</v>
+        <v>-1.068</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4485</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3336</v>
+        <v>-0.386</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-2.0448</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-2.3243</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5216</v>
+        <v>-1.0754</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.679</v>
+        <v>0.6193</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8426</v>
+        <v>-1.6947</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0968</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6861</v>
+        <v>0.0595</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4107</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2598</v>
+        <v>3.0834</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6268</v>
+        <v>1.0726</v>
       </c>
       <c r="L21" t="n">
-        <v>0.633</v>
+        <v>2.0109</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.163</v>
+        <v>-2.1353</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9407</v>
+        <v>-1.0131</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7776999999999999</v>
+        <v>-1.1223</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3895</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3368</v>
+        <v>-1.3632</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3368</v>
+        <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5735</v>
+        <v>-1.2582</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8814</v>
+        <v>-1.101</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6921</v>
+        <v>-0.1572</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0448</v>
+        <v>-1.1548</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3243</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5576</v>
+        <v>-1.2434</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2206</v>
+        <v>-1.1176</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7782</v>
+        <v>-0.1258</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9481000000000001</v>
+        <v>-0.621</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0595</v>
+        <v>0.6127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8885999999999999</v>
+        <v>-1.2337</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0834</v>
+        <v>0.5039</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0726</v>
+        <v>1.0468</v>
       </c>
       <c r="L22" t="n">
-        <v>2.0109</v>
+        <v>-0.5429</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1353</v>
+        <v>-1.1249</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0131</v>
+        <v>-0.4342</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1223</v>
+        <v>-0.6907</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3632</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
         <v>1.7526</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7403</v>
+        <v>-0.8424</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4997</v>
+        <v>-0.6479</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2406</v>
+        <v>-0.1945</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1548</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1548</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9932</v>
+        <v>-1.5667</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2637</v>
+        <v>0.135</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7295</v>
+        <v>-1.7016</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5019</v>
@@ -2248,13 +2248,13 @@
         <v>0.7789</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3617</v>
+        <v>0.0648</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6183</v>
+        <v>-0.2196</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2567</v>
+        <v>0.2845</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0748</v>
+        <v>-3.2625</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2121</v>
+        <v>-1.5112</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8626</v>
+        <v>-1.7513</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3543</v>
@@ -2326,13 +2326,13 @@
         <v>0.3895</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1111</v>
+        <v>-0.0766</v>
       </c>
       <c r="T24" t="n">
-        <v>0.108</v>
+        <v>-0.191</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0031</v>
+        <v>0.1144</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2211</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8531</v>
+        <v>-3.6699</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5148</v>
+        <v>-1.4151</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3383</v>
+        <v>-2.2548</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0016</v>
@@ -2404,13 +2404,13 @@
         <v>0.1947</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3246</v>
+        <v>-0.1414</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2473</v>
+        <v>-0.1477</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0772</v>
+        <v>0.0062</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7216</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.3202</v>
+        <v>-5.7629</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1436</v>
+        <v>-1.642</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.1766</v>
+        <v>-4.1209</v>
       </c>
       <c r="G26" t="n">
         <v>-1.3508</v>
@@ -2482,13 +2482,13 @@
         <v>1.7526</v>
       </c>
       <c r="S26" t="n">
-        <v>0.278</v>
+        <v>-0.1647</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4015</v>
+        <v>-0.0969</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1235</v>
+        <v>-0.0678</v>
       </c>
       <c r="V26" t="n">
         <v>-3.6632</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-14.1596</v>
+        <v>-14.1595</v>
       </c>
       <c r="E27" t="n">
         <v>-4.3079</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.851699999999997</v>
+        <v>-9.851600000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8950999999999996</v>
+        <v>-0.8951</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3617</v>
+        <v>-0.3616999999999998</v>
       </c>
       <c r="I27" t="n">
         <v>-0.5333000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>9.478899999999999</v>
+        <v>9.478900000000001</v>
       </c>
       <c r="K27" t="n">
         <v>5.0655</v>
@@ -2545,7 +2545,7 @@
         <v>-10.3739</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.4271</v>
+        <v>-5.427099999999999</v>
       </c>
       <c r="O27" t="n">
         <v>-4.946800000000001</v>
@@ -2563,10 +2563,10 @@
         <v>-5.039099999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.1034</v>
+        <v>-5.1036</v>
       </c>
       <c r="U27" t="n">
-        <v>0.06469999999999998</v>
+        <v>0.0645</v>
       </c>
       <c r="V27" t="n">
         <v>-10.1727</v>
